--- a/enneagram_test_questions.xlsx
+++ b/enneagram_test_questions.xlsx
@@ -1,38 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kalle\Dropbox\Enneagrammi\EG_TESTI_dataa\Uusi_testi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevPhp\EG uusi testi\Uusi_testi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38EB6C2E-AE1D-4991-9C39-75AA2EF3E104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{567B0266-FC06-403F-9981-2E47F38F19C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5220" yWindow="240" windowWidth="32325" windowHeight="20415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22950" yWindow="6240" windowWidth="26160" windowHeight="15135" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="136">
-  <si>
-    <t>Comparison</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>Option A</t>
-  </si>
-  <si>
-    <t>Option B</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="139">
   <si>
     <t>3–7–8 vs 1–5–6</t>
   </si>
@@ -428,22 +429,35 @@
   </si>
   <si>
     <t>Yritän rauhoittaa ilmapiiriä ja hakea tukea läheisiltäni.</t>
+  </si>
+  <si>
+    <t>/* kommentti</t>
+  </si>
+  <si>
+    <t>BvsC</t>
+  </si>
+  <si>
+    <t>BvsD</t>
+  </si>
+  <si>
+    <t>DvsC</t>
+  </si>
+  <si>
+    <t>AvsB</t>
+  </si>
+  <si>
+    <t>AvsC</t>
+  </si>
+  <si>
+    <t>AvsD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -459,7 +473,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -467,30 +481,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
@@ -795,615 +791,900 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.140625" customWidth="1"/>
-    <col min="2" max="2" width="50.140625" customWidth="1"/>
-    <col min="3" max="3" width="70.140625" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="50.140625" customWidth="1"/>
+    <col min="5" max="5" width="70.140625" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <f t="shared" ref="A4:A48" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f>A8+1</f>
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f>A16+1</f>
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f>A24+1</f>
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f>A32+1</f>
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D34" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B36" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="D36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B37" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="D39" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" t="s">
         <v>4</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f>A40+1</f>
+        <v>36</v>
+      </c>
+      <c r="B42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D42" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>138</v>
+      </c>
+      <c r="C43" t="s">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" t="s">
+        <v>84</v>
+      </c>
+      <c r="F43" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B44" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
         <v>5</v>
       </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D44" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
         <v>5</v>
       </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="D45" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
         <v>5</v>
       </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="D46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s">
         <v>5</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B48" t="s">
+        <v>138</v>
+      </c>
+      <c r="C48" t="s">
         <v>5</v>
       </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="D48" t="s">
         <v>47</v>
       </c>
-      <c r="C39" t="s">
+      <c r="E48" t="s">
         <v>89</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F48" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" t="s">
-        <v>48</v>
-      </c>
-      <c r="C40" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D41" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D42" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" t="s">
-        <v>93</v>
-      </c>
-      <c r="D43" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
